--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/8.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/8.xlsx
@@ -426,13 +426,13 @@
         <v>-17.98235369154056</v>
       </c>
       <c r="E2">
-        <v>-8.29695894171104</v>
+        <v>-7.993786663845524</v>
       </c>
       <c r="F2">
-        <v>-0.07957315689762669</v>
+        <v>-0.56565526240571</v>
       </c>
       <c r="G2">
-        <v>-10.62467068221846</v>
+        <v>-12.34208901271726</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-17.57136588288306</v>
       </c>
       <c r="E3">
-        <v>-9.002621989378296</v>
+        <v>-9.591088129727042</v>
       </c>
       <c r="F3">
-        <v>0.3227926702144119</v>
+        <v>-0.8343444324602934</v>
       </c>
       <c r="G3">
-        <v>-10.6509663454369</v>
+        <v>-12.53470648382867</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-17.06080832090526</v>
       </c>
       <c r="E4">
-        <v>-9.403840257983882</v>
+        <v>-11.56384990405852</v>
       </c>
       <c r="F4">
-        <v>0.2821436904828277</v>
+        <v>-0.4798286958773423</v>
       </c>
       <c r="G4">
-        <v>-10.85513430993483</v>
+        <v>-11.75932706034827</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-16.53482275188535</v>
       </c>
       <c r="E5">
-        <v>-9.55359689341754</v>
+        <v>-10.08566541847476</v>
       </c>
       <c r="F5">
-        <v>0.1212653006217846</v>
+        <v>-0.4404918164966996</v>
       </c>
       <c r="G5">
-        <v>-9.764206927833255</v>
+        <v>-11.77680011970454</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-16.0270653854275</v>
       </c>
       <c r="E6">
-        <v>-10.89663812919039</v>
+        <v>-10.36247292066762</v>
       </c>
       <c r="F6">
-        <v>0.4543162790798272</v>
+        <v>-0.3985267771493851</v>
       </c>
       <c r="G6">
-        <v>-9.338758788944897</v>
+        <v>-11.08541585764653</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-15.5766816729367</v>
       </c>
       <c r="E7">
-        <v>-11.36709676537326</v>
+        <v>-11.14362563004274</v>
       </c>
       <c r="F7">
-        <v>0.3660650587949217</v>
+        <v>-0.1215746214809963</v>
       </c>
       <c r="G7">
-        <v>-9.833427124513877</v>
+        <v>-11.89117615754082</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-15.20100446860202</v>
       </c>
       <c r="E8">
-        <v>-12.18795060637363</v>
+        <v>-12.13215527812512</v>
       </c>
       <c r="F8">
-        <v>0.5062642086651142</v>
+        <v>-0.5550190934776187</v>
       </c>
       <c r="G8">
-        <v>-9.953116587940686</v>
+        <v>-11.39165787275681</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-14.90903592503864</v>
       </c>
       <c r="E9">
-        <v>-12.94539222584458</v>
+        <v>-12.57246333436492</v>
       </c>
       <c r="F9">
-        <v>0.678605461942108</v>
+        <v>-0.1882549753446588</v>
       </c>
       <c r="G9">
-        <v>-9.445275591670947</v>
+        <v>-10.6107730120446</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-14.69528999108065</v>
       </c>
       <c r="E10">
-        <v>-13.36571612628853</v>
+        <v>-13.48770415910715</v>
       </c>
       <c r="F10">
-        <v>0.7094069582914899</v>
+        <v>0.1276896036677647</v>
       </c>
       <c r="G10">
-        <v>-8.915402914837358</v>
+        <v>-10.25797148447001</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-14.54305724191168</v>
       </c>
       <c r="E11">
-        <v>-14.19175054155367</v>
+        <v>-13.18802786317556</v>
       </c>
       <c r="F11">
-        <v>0.9497565028422421</v>
+        <v>0.06229680271335445</v>
       </c>
       <c r="G11">
-        <v>-9.37412534694093</v>
+        <v>-11.21929100870912</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-14.43013810669646</v>
       </c>
       <c r="E12">
-        <v>-13.88101571209535</v>
+        <v>-14.16579332854171</v>
       </c>
       <c r="F12">
-        <v>1.130679066622045</v>
+        <v>0.5614729887302911</v>
       </c>
       <c r="G12">
-        <v>-9.041590979157759</v>
+        <v>-10.40325146491539</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-14.324566682083</v>
       </c>
       <c r="E13">
-        <v>-14.99022466400813</v>
+        <v>-14.79954420896716</v>
       </c>
       <c r="F13">
-        <v>1.453546024190854</v>
+        <v>0.6341096605419213</v>
       </c>
       <c r="G13">
-        <v>-8.461417873400482</v>
+        <v>-9.973251325910534</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-14.20109997647747</v>
       </c>
       <c r="E14">
-        <v>-15.55217206056796</v>
+        <v>-16.79887454030164</v>
       </c>
       <c r="F14">
-        <v>1.947538740746557</v>
+        <v>0.5667562316641971</v>
       </c>
       <c r="G14">
-        <v>-7.810399093102803</v>
+        <v>-9.986493508067619</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-14.03766869197675</v>
       </c>
       <c r="E15">
-        <v>-16.49806159739412</v>
+        <v>-15.63293739449477</v>
       </c>
       <c r="F15">
-        <v>1.899875527515492</v>
+        <v>0.8218611642290987</v>
       </c>
       <c r="G15">
-        <v>-8.378405944003257</v>
+        <v>-7.880715080356923</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-13.82335711397063</v>
       </c>
       <c r="E16">
-        <v>-16.26038916757555</v>
+        <v>-16.74952775904005</v>
       </c>
       <c r="F16">
-        <v>2.355534642387983</v>
+        <v>1.11824539147993</v>
       </c>
       <c r="G16">
-        <v>-7.545588555416501</v>
+        <v>-7.543151993899597</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-13.56243918565053</v>
       </c>
       <c r="E17">
-        <v>-16.498582371905</v>
+        <v>-17.7665550940527</v>
       </c>
       <c r="F17">
-        <v>2.676890744513463</v>
+        <v>1.728765605587752</v>
       </c>
       <c r="G17">
-        <v>-7.188274754271883</v>
+        <v>-8.318571143926469</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-13.26247730618148</v>
       </c>
       <c r="E18">
-        <v>-18.20550460809019</v>
+        <v>-19.27633021431397</v>
       </c>
       <c r="F18">
-        <v>2.651448508981928</v>
+        <v>1.292481548884747</v>
       </c>
       <c r="G18">
-        <v>-6.93741485548807</v>
+        <v>-7.874580639472654</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-12.93596385535977</v>
       </c>
       <c r="E19">
-        <v>-19.95427447258027</v>
+        <v>-20.16036532466935</v>
       </c>
       <c r="F19">
-        <v>3.01407281985193</v>
+        <v>2.42127585864379</v>
       </c>
       <c r="G19">
-        <v>-6.680168914359002</v>
+        <v>-7.135560937650069</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-12.5919605419512</v>
       </c>
       <c r="E20">
-        <v>-19.22615925078299</v>
+        <v>-20.42738226605763</v>
       </c>
       <c r="F20">
-        <v>3.338024615972815</v>
+        <v>2.278766081842971</v>
       </c>
       <c r="G20">
-        <v>-6.344777545775439</v>
+        <v>-7.634013226770435</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-12.24148573594498</v>
       </c>
       <c r="E21">
-        <v>-20.1475859710197</v>
+        <v>-20.43115448490601</v>
       </c>
       <c r="F21">
-        <v>3.537577896141847</v>
+        <v>2.507188737144549</v>
       </c>
       <c r="G21">
-        <v>-6.167213125231089</v>
+        <v>-7.680533012688273</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-11.89375488041354</v>
       </c>
       <c r="E22">
-        <v>-21.34345633001728</v>
+        <v>-21.53039173705391</v>
       </c>
       <c r="F22">
-        <v>4.070938374343545</v>
+        <v>2.938433441624626</v>
       </c>
       <c r="G22">
-        <v>-6.547661018604134</v>
+        <v>-8.054164492795959</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-11.561643429418</v>
       </c>
       <c r="E23">
-        <v>-21.47656629499874</v>
+        <v>-22.68780629477835</v>
       </c>
       <c r="F23">
-        <v>4.181284667707703</v>
+        <v>2.974565692085377</v>
       </c>
       <c r="G23">
-        <v>-6.132313354156092</v>
+        <v>-6.975837047016851</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-11.25575380670406</v>
       </c>
       <c r="E24">
-        <v>-21.50276804560712</v>
+        <v>-22.13701705817342</v>
       </c>
       <c r="F24">
-        <v>4.096839884590556</v>
+        <v>2.590618364769899</v>
       </c>
       <c r="G24">
-        <v>-6.546522190938624</v>
+        <v>-6.674209932388314</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-10.98045317502307</v>
       </c>
       <c r="E25">
-        <v>-23.03897134017715</v>
+        <v>-23.64161160416991</v>
       </c>
       <c r="F25">
-        <v>4.302142017232634</v>
+        <v>2.994447536147804</v>
       </c>
       <c r="G25">
-        <v>-6.728413494502801</v>
+        <v>-6.934968362334549</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-10.73814191565499</v>
       </c>
       <c r="E26">
-        <v>-22.17426828536051</v>
+        <v>-22.99204729250967</v>
       </c>
       <c r="F26">
-        <v>4.077708717132047</v>
+        <v>2.965931327434401</v>
       </c>
       <c r="G26">
-        <v>-6.756804733047591</v>
+        <v>-6.902988492425189</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-10.5228998408832</v>
       </c>
       <c r="E27">
-        <v>-21.4776621857086</v>
+        <v>-23.00189219500235</v>
       </c>
       <c r="F27">
-        <v>3.825056945030162</v>
+        <v>2.93816104420717</v>
       </c>
       <c r="G27">
-        <v>-6.132680824710952</v>
+        <v>-6.442451881366096</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-10.33077040620131</v>
       </c>
       <c r="E28">
-        <v>-22.07781631747114</v>
+        <v>-22.63754476176721</v>
       </c>
       <c r="F28">
-        <v>3.983970747703102</v>
+        <v>2.74488240687511</v>
       </c>
       <c r="G28">
-        <v>-6.472574535227924</v>
+        <v>-6.580514872535861</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-10.15419911287641</v>
       </c>
       <c r="E29">
-        <v>-22.97154689067695</v>
+        <v>-23.1246047836622</v>
       </c>
       <c r="F29">
-        <v>3.917822519027027</v>
+        <v>2.565820697545949</v>
       </c>
       <c r="G29">
-        <v>-6.298790757689423</v>
+        <v>-7.194462163884781</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.986974055728551</v>
       </c>
       <c r="E30">
-        <v>-22.48919648174994</v>
+        <v>-23.90237472295359</v>
       </c>
       <c r="F30">
-        <v>4.159910972672932</v>
+        <v>2.990462932064558</v>
       </c>
       <c r="G30">
-        <v>-6.055396139096666</v>
+        <v>-6.731111589117307</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.824438211118492</v>
       </c>
       <c r="E31">
-        <v>-22.97982494116297</v>
+        <v>-23.23351911202068</v>
       </c>
       <c r="F31">
-        <v>3.872840519910801</v>
+        <v>2.718889041685002</v>
       </c>
       <c r="G31">
-        <v>-5.594147760746629</v>
+        <v>-7.220549262734238</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.663576333423322</v>
       </c>
       <c r="E32">
-        <v>-22.23493172316726</v>
+        <v>-21.1811739354784</v>
       </c>
       <c r="F32">
-        <v>3.68403110067211</v>
+        <v>2.311062596576528</v>
       </c>
       <c r="G32">
-        <v>-5.746753978470412</v>
+        <v>-6.324718950352994</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.503972449674345</v>
       </c>
       <c r="E33">
-        <v>-21.89257455971338</v>
+        <v>-22.75119587393771</v>
       </c>
       <c r="F33">
-        <v>3.627400944547826</v>
+        <v>2.633530460254646</v>
       </c>
       <c r="G33">
-        <v>-5.432195872965482</v>
+        <v>-5.580389133485418</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.344258557430013</v>
       </c>
       <c r="E34">
-        <v>-22.55692886748266</v>
+        <v>-21.27958673261309</v>
       </c>
       <c r="F34">
-        <v>3.491286172233552</v>
+        <v>2.642614597385607</v>
       </c>
       <c r="G34">
-        <v>-5.01703359906764</v>
+        <v>-6.668439651513364</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-9.186441340036026</v>
       </c>
       <c r="E35">
-        <v>-21.02514989201813</v>
+        <v>-21.86389120534879</v>
       </c>
       <c r="F35">
-        <v>3.68930959248827</v>
+        <v>2.255555287946291</v>
       </c>
       <c r="G35">
-        <v>-5.660501024990241</v>
+        <v>-6.387453788322183</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.030199403842092</v>
       </c>
       <c r="E36">
-        <v>-21.74759546435781</v>
+        <v>-21.62891774603879</v>
       </c>
       <c r="F36">
-        <v>3.640048419988525</v>
+        <v>2.75531744515194</v>
       </c>
       <c r="G36">
-        <v>-4.974066028513439</v>
+        <v>-5.591489392678594</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-8.880469133889102</v>
       </c>
       <c r="E37">
-        <v>-20.79431545795114</v>
+        <v>-21.6267984202032</v>
       </c>
       <c r="F37">
-        <v>3.602191513785861</v>
+        <v>2.393380462649239</v>
       </c>
       <c r="G37">
-        <v>-5.09270935954984</v>
+        <v>-4.768659919983819</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-8.739304966442013</v>
       </c>
       <c r="E38">
-        <v>-20.68048773529434</v>
+        <v>-21.3190297412199</v>
       </c>
       <c r="F38">
-        <v>3.403498185928913</v>
+        <v>2.690531203563143</v>
       </c>
       <c r="G38">
-        <v>-4.397799366492504</v>
+        <v>-6.060474515953907</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-8.607145776776536</v>
       </c>
       <c r="E39">
-        <v>-21.04237620714331</v>
+        <v>-21.10760434674979</v>
       </c>
       <c r="F39">
-        <v>3.837976817888317</v>
+        <v>2.267022902479988</v>
       </c>
       <c r="G39">
-        <v>-4.082241476234713</v>
+        <v>-4.918392584179515</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-8.485480538740653</v>
       </c>
       <c r="E40">
-        <v>-19.87526618656845</v>
+        <v>-20.21966116332579</v>
       </c>
       <c r="F40">
-        <v>3.349566664684537</v>
+        <v>2.665044624265976</v>
       </c>
       <c r="G40">
-        <v>-3.658528063208933</v>
+        <v>-4.487650882973862</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-8.372569561284326</v>
       </c>
       <c r="E41">
-        <v>-20.72668269864658</v>
+        <v>-20.05729272778077</v>
       </c>
       <c r="F41">
-        <v>3.939590556834743</v>
+        <v>2.811052807434001</v>
       </c>
       <c r="G41">
-        <v>-4.166782877671081</v>
+        <v>-4.930055636114368</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-8.267763367063122</v>
       </c>
       <c r="E42">
-        <v>-20.54165830764119</v>
+        <v>-20.78699744395474</v>
       </c>
       <c r="F42">
-        <v>3.634811104526167</v>
+        <v>2.813642166605744</v>
       </c>
       <c r="G42">
-        <v>-4.467506213367398</v>
+        <v>-5.538010840037207</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-8.167842005368776</v>
       </c>
       <c r="E43">
-        <v>-20.11969057113246</v>
+        <v>-19.78433442849443</v>
       </c>
       <c r="F43">
-        <v>3.672560318726582</v>
+        <v>2.711998337246925</v>
       </c>
       <c r="G43">
-        <v>-3.796544706741149</v>
+        <v>-5.557973429639013</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.070267179065658</v>
       </c>
       <c r="E44">
-        <v>-20.34017744209192</v>
+        <v>-19.56969834595288</v>
       </c>
       <c r="F44">
-        <v>3.935604369045582</v>
+        <v>2.171359146657868</v>
       </c>
       <c r="G44">
-        <v>-4.299813839621155</v>
+        <v>-4.953375118892994</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-7.970763178045117</v>
       </c>
       <c r="E45">
-        <v>-19.81490615652021</v>
+        <v>-19.61592953709718</v>
       </c>
       <c r="F45">
-        <v>3.602696715972886</v>
+        <v>2.553082950868069</v>
       </c>
       <c r="G45">
-        <v>-4.465251731855154</v>
+        <v>-5.381726606219293</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-7.868529540672807</v>
       </c>
       <c r="E46">
-        <v>-20.04043321905021</v>
+        <v>-19.56279695156519</v>
       </c>
       <c r="F46">
-        <v>3.228422664388912</v>
+        <v>2.761758377110032</v>
       </c>
       <c r="G46">
-        <v>-4.204870704100396</v>
+        <v>-5.41962573155287</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-7.763929511063093</v>
       </c>
       <c r="E47">
-        <v>-19.42294861726031</v>
+        <v>-19.70025878006802</v>
       </c>
       <c r="F47">
-        <v>3.508917570190139</v>
+        <v>2.254438775275906</v>
       </c>
       <c r="G47">
-        <v>-4.143264762160099</v>
+        <v>-5.314433147042528</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.658235365056655</v>
       </c>
       <c r="E48">
-        <v>-18.59191929516471</v>
+        <v>-18.92911852672386</v>
       </c>
       <c r="F48">
-        <v>3.557317206671884</v>
+        <v>2.540875745671862</v>
       </c>
       <c r="G48">
-        <v>-4.743102508420646</v>
+        <v>-6.06727768703711</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.55682012383286</v>
       </c>
       <c r="E49">
-        <v>-18.01251915977932</v>
+        <v>-18.04436338900125</v>
       </c>
       <c r="F49">
-        <v>3.434372532750404</v>
+        <v>2.362756341362387</v>
       </c>
       <c r="G49">
-        <v>-4.740579872719721</v>
+        <v>-6.506371894638344</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.463217300770461</v>
       </c>
       <c r="E50">
-        <v>-18.04334448234953</v>
+        <v>-18.44314986706472</v>
       </c>
       <c r="F50">
-        <v>3.685412092230373</v>
+        <v>2.665153899974142</v>
       </c>
       <c r="G50">
-        <v>-4.835767988610385</v>
+        <v>-6.140526817639024</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.381919374632351</v>
       </c>
       <c r="E51">
-        <v>-17.41214313279039</v>
+        <v>-17.73115601273474</v>
       </c>
       <c r="F51">
-        <v>3.701372680446172</v>
+        <v>2.414657551623169</v>
       </c>
       <c r="G51">
-        <v>-4.588526516100995</v>
+        <v>-5.311235160051591</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.309613860032584</v>
       </c>
       <c r="E52">
-        <v>-18.45119243690234</v>
+        <v>-17.50866302778988</v>
       </c>
       <c r="F52">
-        <v>3.222119514845463</v>
+        <v>2.242630663970389</v>
       </c>
       <c r="G52">
-        <v>-5.162452622425666</v>
+        <v>-6.707113444503131</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.240804397879578</v>
       </c>
       <c r="E53">
-        <v>-17.91286103229251</v>
+        <v>-18.29710658031735</v>
       </c>
       <c r="F53">
-        <v>3.057542379818912</v>
+        <v>2.423985579465107</v>
       </c>
       <c r="G53">
-        <v>-5.149034981354999</v>
+        <v>-5.595567984782976</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.174243102532827</v>
       </c>
       <c r="E54">
-        <v>-17.29394543271619</v>
+        <v>-17.25382315300823</v>
       </c>
       <c r="F54">
-        <v>3.223696885937241</v>
+        <v>2.359288025407575</v>
       </c>
       <c r="G54">
-        <v>-5.458309456179253</v>
+        <v>-6.681039587835831</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.11292834579951</v>
       </c>
       <c r="E55">
-        <v>-17.43146160290712</v>
+        <v>-17.20989242665982</v>
       </c>
       <c r="F55">
-        <v>3.358004649801999</v>
+        <v>1.737278024883239</v>
       </c>
       <c r="G55">
-        <v>-4.990996158401272</v>
+        <v>-5.632970528285662</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.061094017816602</v>
       </c>
       <c r="E56">
-        <v>-18.69184460261796</v>
+        <v>-16.331499794918</v>
       </c>
       <c r="F56">
-        <v>3.079427611864369</v>
+        <v>1.988873465139527</v>
       </c>
       <c r="G56">
-        <v>-4.948564896224433</v>
+        <v>-6.352295794695123</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.020191593150236</v>
       </c>
       <c r="E57">
-        <v>-16.22580521157897</v>
+        <v>-15.64916291686425</v>
       </c>
       <c r="F57">
-        <v>3.331415811187686</v>
+        <v>2.38529247653909</v>
       </c>
       <c r="G57">
-        <v>-5.811657223767824</v>
+        <v>-6.555159404250583</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.99401843279866</v>
       </c>
       <c r="E58">
-        <v>-17.61697959757935</v>
+        <v>-17.20271932383167</v>
       </c>
       <c r="F58">
-        <v>2.950273227048451</v>
+        <v>2.280411552289113</v>
       </c>
       <c r="G58">
-        <v>-5.835128991641257</v>
+        <v>-6.944568944398435</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.984172336676419</v>
       </c>
       <c r="E59">
-        <v>-16.83751148053508</v>
+        <v>-14.89328814939994</v>
       </c>
       <c r="F59">
-        <v>3.324713567753546</v>
+        <v>1.563675349844598</v>
       </c>
       <c r="G59">
-        <v>-4.789287929239018</v>
+        <v>-7.222568695513194</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.994852858341893</v>
       </c>
       <c r="E60">
-        <v>-17.02572844571588</v>
+        <v>-16.22115446877309</v>
       </c>
       <c r="F60">
-        <v>2.823543495989072</v>
+        <v>2.168651009542466</v>
       </c>
       <c r="G60">
-        <v>-5.669108443392346</v>
+        <v>-6.756513405040135</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.02708145724553</v>
       </c>
       <c r="E61">
-        <v>-16.83814999537016</v>
+        <v>-15.61419856905102</v>
       </c>
       <c r="F61">
-        <v>3.078865396264388</v>
+        <v>1.722228067568818</v>
       </c>
       <c r="G61">
-        <v>-6.21812931562508</v>
+        <v>-6.415249128669904</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.079032751716057</v>
       </c>
       <c r="E62">
-        <v>-17.11293326968159</v>
+        <v>-15.71623867386586</v>
       </c>
       <c r="F62">
-        <v>3.514264161360663</v>
+        <v>2.493141265674601</v>
       </c>
       <c r="G62">
-        <v>-6.160837014522452</v>
+        <v>-6.979236977285683</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.14864636229372</v>
       </c>
       <c r="E63">
-        <v>-16.49896729219565</v>
+        <v>-15.99241218969765</v>
       </c>
       <c r="F63">
-        <v>2.791039515780592</v>
+        <v>1.961891867458185</v>
       </c>
       <c r="G63">
-        <v>-5.747647825766016</v>
+        <v>-7.551312488653901</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.230426226155316</v>
       </c>
       <c r="E64">
-        <v>-16.05287184617405</v>
+        <v>-15.20363805856761</v>
       </c>
       <c r="F64">
-        <v>2.837031919270869</v>
+        <v>2.025941685796302</v>
       </c>
       <c r="G64">
-        <v>-6.113526008220728</v>
+        <v>-7.23657230314431</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.318271795333334</v>
       </c>
       <c r="E65">
-        <v>-15.56639146895205</v>
+        <v>-14.877972850306</v>
       </c>
       <c r="F65">
-        <v>3.284107348081679</v>
+        <v>2.260349165752326</v>
       </c>
       <c r="G65">
-        <v>-6.027203533284232</v>
+        <v>-6.791886584127248</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.402704093308902</v>
       </c>
       <c r="E66">
-        <v>-16.14692825131337</v>
+        <v>-15.30355883754686</v>
       </c>
       <c r="F66">
-        <v>2.919427386933438</v>
+        <v>1.748823241006793</v>
       </c>
       <c r="G66">
-        <v>-5.973357510087986</v>
+        <v>-7.464321283518472</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.475945594666235</v>
       </c>
       <c r="E67">
-        <v>-17.00551786621965</v>
+        <v>-15.23599400535242</v>
       </c>
       <c r="F67">
-        <v>3.264974596917255</v>
+        <v>1.960099112361908</v>
       </c>
       <c r="G67">
-        <v>-6.38642420865947</v>
+        <v>-7.096655406472554</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.531598843897257</v>
       </c>
       <c r="E68">
-        <v>-16.39707209854906</v>
+        <v>-16.23784642396537</v>
       </c>
       <c r="F68">
-        <v>2.649277248171861</v>
+        <v>1.716623332334078</v>
       </c>
       <c r="G68">
-        <v>-6.497512874775254</v>
+        <v>-7.417592933231659</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.570814615114967</v>
       </c>
       <c r="E69">
-        <v>-16.66565589194399</v>
+        <v>-15.27982510527266</v>
       </c>
       <c r="F69">
-        <v>2.703435239362144</v>
+        <v>1.713297549911655</v>
       </c>
       <c r="G69">
-        <v>-7.041918846526244</v>
+        <v>-7.753365014552239</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.597422570052043</v>
       </c>
       <c r="E70">
-        <v>-16.68971114587274</v>
+        <v>-14.39061394912651</v>
       </c>
       <c r="F70">
-        <v>2.93706036859594</v>
+        <v>1.639935540790753</v>
       </c>
       <c r="G70">
-        <v>-6.849099432136932</v>
+        <v>-7.289454957588629</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.613770383924684</v>
       </c>
       <c r="E71">
-        <v>-15.63870214190653</v>
+        <v>-14.87877439020536</v>
       </c>
       <c r="F71">
-        <v>2.91844390555995</v>
+        <v>1.672844949713585</v>
       </c>
       <c r="G71">
-        <v>-6.811534671902822</v>
+        <v>-7.797752809142787</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.623632348454892</v>
       </c>
       <c r="E72">
-        <v>-17.58690600169441</v>
+        <v>-15.50881192194452</v>
       </c>
       <c r="F72">
-        <v>2.691932783298307</v>
+        <v>1.904827775913071</v>
       </c>
       <c r="G72">
-        <v>-6.970569969063871</v>
+        <v>-7.908172745059638</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-7.626010501072185</v>
       </c>
       <c r="E73">
-        <v>-17.48193597419661</v>
+        <v>-15.33444303027917</v>
       </c>
       <c r="F73">
-        <v>2.70942323142842</v>
+        <v>1.42569338825602</v>
       </c>
       <c r="G73">
-        <v>-6.924659323525258</v>
+        <v>-7.991532281738487</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.620601074608068</v>
       </c>
       <c r="E74">
-        <v>-16.85416720793529</v>
+        <v>-16.29815211232551</v>
       </c>
       <c r="F74">
-        <v>2.727987432169201</v>
+        <v>1.262452901022099</v>
       </c>
       <c r="G74">
-        <v>-7.659395179420026</v>
+        <v>-7.509238765395303</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.605730596905694</v>
       </c>
       <c r="E75">
-        <v>-17.57422627447293</v>
+        <v>-16.18421570629252</v>
       </c>
       <c r="F75">
-        <v>2.682734619341435</v>
+        <v>1.508720754578849</v>
       </c>
       <c r="G75">
-        <v>-7.557367476445228</v>
+        <v>-7.941288132088968</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-7.581036749069406</v>
       </c>
       <c r="E76">
-        <v>-17.27459979175542</v>
+        <v>-16.66440150464387</v>
       </c>
       <c r="F76">
-        <v>2.543959221089222</v>
+        <v>1.644732586008619</v>
       </c>
       <c r="G76">
-        <v>-7.005694857235538</v>
+        <v>-7.887670536534932</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.546532835472325</v>
       </c>
       <c r="E77">
-        <v>-17.84670002704045</v>
+        <v>-16.70702803047807</v>
       </c>
       <c r="F77">
-        <v>2.465885686869888</v>
+        <v>1.721271509195893</v>
       </c>
       <c r="G77">
-        <v>-7.491706116219324</v>
+        <v>-8.282681519735231</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-7.503505071778925</v>
       </c>
       <c r="E78">
-        <v>-17.89346104964365</v>
+        <v>-17.77420368665166</v>
       </c>
       <c r="F78">
-        <v>2.459191361965326</v>
+        <v>1.117306253872074</v>
       </c>
       <c r="G78">
-        <v>-7.051492944225815</v>
+        <v>-8.333385835214708</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-7.453162208057623</v>
       </c>
       <c r="E79">
-        <v>-18.44612054601375</v>
+        <v>-17.4063014013205</v>
       </c>
       <c r="F79">
-        <v>2.606612210809922</v>
+        <v>1.745809448649711</v>
       </c>
       <c r="G79">
-        <v>-6.978319956171305</v>
+        <v>-7.556341207328054</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.393839323933028</v>
       </c>
       <c r="E80">
-        <v>-18.92357114606446</v>
+        <v>-18.18912964607846</v>
       </c>
       <c r="F80">
-        <v>2.412440363341553</v>
+        <v>1.045914374909979</v>
       </c>
       <c r="G80">
-        <v>-8.319736455956294</v>
+        <v>-8.129274149990943</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.324515712376396</v>
       </c>
       <c r="E81">
-        <v>-20.27523006787391</v>
+        <v>-18.27138484795378</v>
       </c>
       <c r="F81">
-        <v>2.15055400204674</v>
+        <v>1.180716255020354</v>
       </c>
       <c r="G81">
-        <v>-7.67264398266819</v>
+        <v>-7.561247435817254</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-7.240669382031201</v>
       </c>
       <c r="E82">
-        <v>-20.20782826074374</v>
+        <v>-18.41416763341563</v>
       </c>
       <c r="F82">
-        <v>2.383099043846207</v>
+        <v>1.330734381566271</v>
       </c>
       <c r="G82">
-        <v>-7.254138057775684</v>
+        <v>-8.040832925909314</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-7.139418846457673</v>
       </c>
       <c r="E83">
-        <v>-20.62572037064557</v>
+        <v>-20.97100292830842</v>
       </c>
       <c r="F83">
-        <v>2.324376812207627</v>
+        <v>1.500547248349266</v>
       </c>
       <c r="G83">
-        <v>-7.299638195667427</v>
+        <v>-7.368216146513429</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-7.016510199876934</v>
       </c>
       <c r="E84">
-        <v>-20.81494265705608</v>
+        <v>-21.169128194618</v>
       </c>
       <c r="F84">
-        <v>2.245964364922389</v>
+        <v>1.303486721291135</v>
       </c>
       <c r="G84">
-        <v>-7.734667053346436</v>
+        <v>-8.263907415982024</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.869971561442317</v>
       </c>
       <c r="E85">
-        <v>-22.5846385999356</v>
+        <v>-21.63359565968872</v>
       </c>
       <c r="F85">
-        <v>1.862953007802936</v>
+        <v>1.102386160442719</v>
       </c>
       <c r="G85">
-        <v>-7.359453132470978</v>
+        <v>-8.442382236549673</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.701370188054801</v>
       </c>
       <c r="E86">
-        <v>-23.57759256712347</v>
+        <v>-21.97240249952059</v>
       </c>
       <c r="F86">
-        <v>2.183636034914354</v>
+        <v>1.19545897338718</v>
       </c>
       <c r="G86">
-        <v>-7.036337266747032</v>
+        <v>-7.720689930079633</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.5143798904443</v>
       </c>
       <c r="E87">
-        <v>-25.24549294278457</v>
+        <v>-23.48442827136367</v>
       </c>
       <c r="F87">
-        <v>1.978560372218185</v>
+        <v>0.9859980290111585</v>
       </c>
       <c r="G87">
-        <v>-7.297999475625487</v>
+        <v>-8.185649429979193</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.315124322258012</v>
       </c>
       <c r="E88">
-        <v>-26.87630058784884</v>
+        <v>-25.67115138560956</v>
       </c>
       <c r="F88">
-        <v>2.085140612915429</v>
+        <v>1.159093918156859</v>
       </c>
       <c r="G88">
-        <v>-6.849404002326545</v>
+        <v>-7.370281926929935</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.107943512494878</v>
       </c>
       <c r="E89">
-        <v>-28.07915385376624</v>
+        <v>-27.54730269546139</v>
       </c>
       <c r="F89">
-        <v>1.95879255498167</v>
+        <v>0.9927366976813533</v>
       </c>
       <c r="G89">
-        <v>-6.471015268278927</v>
+        <v>-7.735951545015673</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.896549748215453</v>
       </c>
       <c r="E90">
-        <v>-28.55986042662847</v>
+        <v>-27.93966779738198</v>
       </c>
       <c r="F90">
-        <v>1.890967181741145</v>
+        <v>1.10229905661737</v>
       </c>
       <c r="G90">
-        <v>-6.258047873737612</v>
+        <v>-7.448155889650211</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.680809341096346</v>
       </c>
       <c r="E91">
-        <v>-31.2831511048582</v>
+        <v>-29.50199133002825</v>
       </c>
       <c r="F91">
-        <v>1.970510395050006</v>
+        <v>1.182220775640021</v>
       </c>
       <c r="G91">
-        <v>-6.615229253060659</v>
+        <v>-7.713681505172996</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.462578658262193</v>
       </c>
       <c r="E92">
-        <v>-32.89968273561328</v>
+        <v>-31.41506781693863</v>
       </c>
       <c r="F92">
-        <v>2.03548193023091</v>
+        <v>1.101977564316535</v>
       </c>
       <c r="G92">
-        <v>-6.063487112394644</v>
+        <v>-7.46891632072698</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.242409304771361</v>
       </c>
       <c r="E93">
-        <v>-35.32888299059988</v>
+        <v>-33.72379254942517</v>
       </c>
       <c r="F93">
-        <v>2.019144420007236</v>
+        <v>1.129812779486299</v>
       </c>
       <c r="G93">
-        <v>-6.758128951263299</v>
+        <v>-6.670508742475409</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-5.021169580705014</v>
       </c>
       <c r="E94">
-        <v>-37.7472352861011</v>
+        <v>-35.66065711029784</v>
       </c>
       <c r="F94">
-        <v>1.798588031987646</v>
+        <v>1.091186192208731</v>
       </c>
       <c r="G94">
-        <v>-6.032854634519768</v>
+        <v>-6.14690292834766</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.80199885020297</v>
       </c>
       <c r="E95">
-        <v>-39.560252875575</v>
+        <v>-38.64186249716042</v>
       </c>
       <c r="F95">
-        <v>1.844534508006376</v>
+        <v>1.055915477765979</v>
       </c>
       <c r="G95">
-        <v>-6.097781053635955</v>
+        <v>-7.176760676886298</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.590317831223645</v>
       </c>
       <c r="E96">
-        <v>-40.98806261629743</v>
+        <v>-39.89362781083467</v>
       </c>
       <c r="F96">
-        <v>2.308701291056608</v>
+        <v>1.396093924696457</v>
       </c>
       <c r="G96">
-        <v>-6.223840006680323</v>
+        <v>-6.459468085437949</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.392468148487684</v>
       </c>
       <c r="E97">
-        <v>-44.11060167693941</v>
+        <v>-42.33171972453533</v>
       </c>
       <c r="F97">
-        <v>1.932444439666504</v>
+        <v>1.722910644818372</v>
       </c>
       <c r="G97">
-        <v>-6.193389608810106</v>
+        <v>-6.643494690874956</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.217612118469617</v>
       </c>
       <c r="E98">
-        <v>-45.59416598964428</v>
+        <v>-44.72353063387759</v>
       </c>
       <c r="F98">
-        <v>2.204788011120964</v>
+        <v>1.390110683747927</v>
       </c>
       <c r="G98">
-        <v>-6.372010093381483</v>
+        <v>-6.849387449598849</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.067351238637127</v>
       </c>
       <c r="E99">
-        <v>-48.26537242407478</v>
+        <v>-48.89849158237617</v>
       </c>
       <c r="F99">
-        <v>2.041276710175503</v>
+        <v>1.391032400590713</v>
       </c>
       <c r="G99">
-        <v>-6.009435835374964</v>
+        <v>-6.573102561073433</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.951205088197306</v>
       </c>
       <c r="E100">
-        <v>-51.39976702966884</v>
+        <v>-48.73296227197379</v>
       </c>
       <c r="F100">
-        <v>2.365402713947086</v>
+        <v>1.117890641354871</v>
       </c>
       <c r="G100">
-        <v>-6.352795687071553</v>
+        <v>-7.139917615579749</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.85988055309425</v>
       </c>
       <c r="E101">
-        <v>-52.7203753373262</v>
+        <v>-52.3548697468636</v>
       </c>
       <c r="F101">
-        <v>2.237255566093388</v>
+        <v>1.225234228303357</v>
       </c>
       <c r="G101">
-        <v>-6.745836895675986</v>
+        <v>-6.627455097737188</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.81071799862718</v>
       </c>
       <c r="E102">
-        <v>-55.50482532126652</v>
+        <v>-54.72634327943742</v>
       </c>
       <c r="F102">
-        <v>2.288095693390825</v>
+        <v>1.706571550888784</v>
       </c>
       <c r="G102">
-        <v>-6.457809502122775</v>
+        <v>-6.499264153365528</v>
       </c>
     </row>
   </sheetData>
